--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487505_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487505_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.603</v>
+        <v>3.6997</v>
       </c>
       <c r="E2" t="n">
-        <v>5.303</v>
+        <v>3.8273</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3</v>
+        <v>-0.1277</v>
       </c>
       <c r="G2" t="n">
         <v>2.8755</v>
@@ -610,13 +610,13 @@
         <v>2.3502</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1245</v>
+        <v>0.2211</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4221</v>
+        <v>-0.0535</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7024</v>
+        <v>0.2747</v>
       </c>
       <c r="V2" t="n">
         <v>0.2113</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. CAAMAÑO ARAGUNDE</t>
+          <t>O. CASTAÑO RUBIANES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3803</v>
+        <v>0.6798</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.078</v>
+        <v>0.8511</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4583</v>
+        <v>-0.1713</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0419</v>
+        <v>-0.4537</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.231</v>
+        <v>-1.6513</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2729</v>
+        <v>1.1976</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0408</v>
+        <v>2.167</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0408</v>
+        <v>0.1819</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.9852</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001</v>
+        <v>-2.6207</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2719</v>
+        <v>-1.8332</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2729</v>
+        <v>-0.7875</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1958</v>
+        <v>0.3917</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1958</v>
+        <v>2.3502</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1426</v>
+        <v>-0.4748</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1188</v>
+        <v>-0.574</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2614</v>
+        <v>0.0993</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. CASTAÑO RUBIANES</t>
+          <t>C. CAAMAÑO ARAGUNDE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0866</v>
+        <v>0.3268</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1777</v>
+        <v>-0.078</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0911</v>
+        <v>0.4048</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4537</v>
+        <v>0.0419</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.6513</v>
+        <v>-0.231</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1976</v>
+        <v>0.2729</v>
       </c>
       <c r="J4" t="n">
-        <v>2.167</v>
+        <v>0.0408</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1819</v>
+        <v>0.0408</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9852</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.6207</v>
+        <v>0.001</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.8332</v>
+        <v>-0.2719</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7875</v>
+        <v>0.2729</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3917</v>
+        <v>0.1958</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3502</v>
+        <v>0.1958</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.068</v>
+        <v>0.0891</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2474</v>
+        <v>-0.1188</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1794</v>
+        <v>0.2079</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.479</v>
+        <v>-0.0207</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0524</v>
+        <v>0.5641</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5314</v>
+        <v>-0.5848</v>
       </c>
       <c r="G5" t="n">
         <v>-1.5209</v>
@@ -844,13 +844,13 @@
         <v>2.3502</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1866</v>
+        <v>-0.7284</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2474</v>
+        <v>-0.7358</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0608</v>
+        <v>0.0074</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1217</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3896</v>
+        <v>-1.3256</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.766</v>
+        <v>-0.8089</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6237</v>
+        <v>-0.5167</v>
       </c>
       <c r="G6" t="n">
         <v>-2.4944</v>
@@ -922,13 +922,13 @@
         <v>1.9585</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5404</v>
+        <v>-0.4764</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.387</v>
+        <v>-0.4299</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1534</v>
+        <v>-0.0465</v>
       </c>
       <c r="V6" t="n">
         <v>0.6659</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. REY MARIÑO</t>
+          <t>A. MONTEAGUDO FERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2808</v>
+        <v>-2.2645</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3837</v>
+        <v>-1.3933</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8971</v>
+        <v>-0.8713</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7437</v>
+        <v>-2.0284</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0215</v>
+        <v>-0.4975</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7223000000000001</v>
+        <v>-1.531</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0114</v>
+        <v>-0.2785</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9306</v>
+        <v>0.3181</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0808</v>
+        <v>-0.5966</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7551</v>
+        <v>-1.7499</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.952</v>
+        <v>-0.8156</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8031</v>
+        <v>-0.9344</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3917</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5875</v>
+        <v>1.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0713</v>
+        <v>-0.061</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4158</v>
+        <v>-0.3729</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4871</v>
+        <v>0.3119</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2166</v>
+        <v>0.6083</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2166</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. LOPEZ CAMIÑA</t>
+          <t>D. REY MARIÑO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.329</v>
+        <v>-2.2794</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0752</v>
+        <v>-0.2219</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4042</v>
+        <v>-2.0575</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.0172</v>
+        <v>-0.7437</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4814</v>
+        <v>-0.0215</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.5358</v>
+        <v>-0.7223000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1319</v>
+        <v>1.0114</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4695</v>
+        <v>0.9306</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6014</v>
+        <v>0.0808</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8853</v>
+        <v>-1.7551</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.951</v>
+        <v>-0.952</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9344</v>
+        <v>-0.8031</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5875</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R8" t="n">
         <v>0.5875</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4389</v>
+        <v>0.0726</v>
       </c>
       <c r="T8" t="n">
-        <v>0.207</v>
+        <v>-0.2541</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2318</v>
+        <v>0.3267</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.3383</v>
+        <v>-1.2166</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.3383</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MONTEAGUDO FERNANDEZ</t>
+          <t>B. LOPEZ CAMIÑA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6134</v>
+        <v>-2.4268</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.555</v>
+        <v>-0.1295</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0584</v>
+        <v>-2.2973</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0284</v>
+        <v>-2.0172</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4975</v>
+        <v>-0.4814</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.531</v>
+        <v>-1.5358</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2785</v>
+        <v>-0.1319</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3181</v>
+        <v>0.4695</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5966</v>
+        <v>-0.6014</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7499</v>
+        <v>-1.8853</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8156</v>
+        <v>-0.951</v>
       </c>
       <c r="O9" t="n">
         <v>-0.9344</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7834</v>
+        <v>0.5875</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1751</v>
+        <v>0.5875</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4099</v>
+        <v>0.3411</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5346</v>
+        <v>0.0023</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1247</v>
+        <v>0.3388</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6083</v>
+        <v>-1.3383</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6083</v>
+        <v>-1.3383</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0707</v>
+        <v>-3.973</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5826</v>
+        <v>-3.3779</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4882</v>
+        <v>-0.5951</v>
       </c>
       <c r="G10" t="n">
         <v>-4.9582</v>
@@ -1234,13 +1234,13 @@
         <v>1.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.166</v>
+        <v>-0.0682</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7128</v>
+        <v>-0.5082</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.4399</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1217</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.519</v>
+        <v>-5.2296</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.7338</v>
+        <v>-4.6315</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7852</v>
+        <v>-0.5981</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6049</v>
@@ -1312,13 +1312,13 @@
         <v>1.7626</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1515</v>
+        <v>-0.8621</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.891</v>
+        <v>-0.7887</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2605</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6083</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.9849</v>
+        <v>-7.4862</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.7241</v>
+        <v>-5.5194</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2608</v>
+        <v>-1.9667</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0377</v>
@@ -1390,13 +1390,13 @@
         <v>1.1751</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1043</v>
+        <v>-0.6056</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.891</v>
+        <v>-0.6864</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2133</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1217</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-20.5965</v>
+        <v>-20.2995</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.2149</v>
+        <v>-10.9179</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.3818</v>
+        <v>-9.3817</v>
       </c>
       <c r="G13" t="n">
         <v>-15.9417</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.832799999999999</v>
+        <v>-7.832800000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.1092</v>
+        <v>-8.109200000000001</v>
       </c>
       <c r="J13" t="n">
         <v>6.932300000000001</v>
@@ -1447,7 +1447,7 @@
         <v>7.114000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1815999999999997</v>
+        <v>-0.1816000000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-22.8739</v>
@@ -1468,13 +1468,13 @@
         <v>15.6678</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.8494</v>
+        <v>-2.5526</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.816700000000001</v>
+        <v>-4.52</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9673</v>
+        <v>1.9674</v>
       </c>
       <c r="V13" t="n">
         <v>-0.8261999999999999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. DIARRA</t>
+          <t>D. CUETOS FERNANDEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.9259</v>
+        <v>5.2622</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9122</v>
+        <v>3.3916</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0137</v>
+        <v>1.8706</v>
       </c>
       <c r="G14" t="n">
-        <v>3.2051</v>
+        <v>2.5629</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4165</v>
+        <v>1.5622</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7887</v>
+        <v>1.0007</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7719</v>
+        <v>2.9515</v>
       </c>
       <c r="K14" t="n">
-        <v>2.004</v>
+        <v>2.1028</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7679</v>
+        <v>0.8487</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4332</v>
+        <v>-0.3886</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4125</v>
+        <v>-0.5406</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0208</v>
+        <v>0.152</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.5668</v>
+        <v>1.5668</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3709</v>
+        <v>1.5668</v>
       </c>
       <c r="S14" t="n">
-        <v>3.6205</v>
+        <v>0.5242</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1943</v>
+        <v>-0.1682</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4262</v>
+        <v>0.6924</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3329</v>
+        <v>0.6083</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8837</v>
+        <v>0.6083</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. CUETOS FERNANDEZ</t>
+          <t>M. BARTOLOME COBLE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.7681</v>
+        <v>4.648</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0846</v>
+        <v>3.1585</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6835</v>
+        <v>1.4895</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5629</v>
+        <v>6.3373</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5622</v>
+        <v>2.74</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0007</v>
+        <v>3.5973</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9515</v>
+        <v>7.8727</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1028</v>
+        <v>4.0284</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8487</v>
+        <v>3.8443</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3886</v>
+        <v>-1.5354</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5406</v>
+        <v>-1.2884</v>
       </c>
       <c r="O15" t="n">
-        <v>0.152</v>
+        <v>-0.2469</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5668</v>
+        <v>-2.3502</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-4.8962</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5668</v>
+        <v>2.546</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0301</v>
+        <v>-0.2228</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4752</v>
+        <v>-0.7017</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5053</v>
+        <v>0.4789</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6083</v>
+        <v>0.8837</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6083</v>
+        <v>0.8837</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. BARTOLOME COBLE</t>
+          <t>A. GOMEZ CABAL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8377</v>
+        <v>4.1018</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7491</v>
+        <v>1.8549</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0886</v>
+        <v>2.2468</v>
       </c>
       <c r="G16" t="n">
-        <v>6.3373</v>
+        <v>2.9249</v>
       </c>
       <c r="H16" t="n">
-        <v>2.74</v>
+        <v>1.1518</v>
       </c>
       <c r="I16" t="n">
-        <v>3.5973</v>
+        <v>1.7731</v>
       </c>
       <c r="J16" t="n">
-        <v>7.8727</v>
+        <v>2.5604</v>
       </c>
       <c r="K16" t="n">
-        <v>4.0284</v>
+        <v>0.8081</v>
       </c>
       <c r="L16" t="n">
-        <v>3.8443</v>
+        <v>1.7523</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5354</v>
+        <v>0.3645</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2884</v>
+        <v>0.3437</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2469</v>
+        <v>0.0208</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.3502</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.8962</v>
+        <v>-1.9585</v>
       </c>
       <c r="R16" t="n">
-        <v>2.546</v>
+        <v>1.3709</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0331</v>
+        <v>0.5478</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.111</v>
+        <v>0.0365</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0779</v>
+        <v>0.5114</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8837</v>
+        <v>1.2166</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8837</v>
+        <v>1.2166</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.509</v>
+        <v>3.4823</v>
       </c>
       <c r="E17" t="n">
         <v>1.4615</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0475</v>
+        <v>2.0208</v>
       </c>
       <c r="G17" t="n">
         <v>1.1173</v>
@@ -1780,13 +1780,13 @@
         <v>2.3502</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0416</v>
+        <v>0.0149</v>
       </c>
       <c r="T17" t="n">
         <v>-0.3694</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4109</v>
+        <v>0.3842</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GOMEZ CABAL</t>
+          <t>. SUAREZ HEVIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.4297</v>
+        <v>3.349</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3433</v>
+        <v>2.3524</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0864</v>
+        <v>0.9966</v>
       </c>
       <c r="G18" t="n">
-        <v>2.9249</v>
+        <v>2.0122</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1518</v>
+        <v>1.0926</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7731</v>
+        <v>0.9195</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5604</v>
+        <v>3.7527</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8081</v>
+        <v>2.4498</v>
       </c>
       <c r="L18" t="n">
-        <v>1.7523</v>
+        <v>1.3029</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3645</v>
+        <v>-1.7406</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3437</v>
+        <v>-1.3572</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0208</v>
+        <v>-0.3834</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5875</v>
+        <v>1.1751</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3709</v>
+        <v>2.1543</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1242</v>
+        <v>0.1617</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4752</v>
+        <v>-0.4211</v>
       </c>
       <c r="U18" t="n">
-        <v>0.351</v>
+        <v>0.5828</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ FERNANDEZ</t>
+          <t>D. DIARRA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.2937</v>
+        <v>3.0388</v>
       </c>
       <c r="E19" t="n">
-        <v>2.113</v>
+        <v>1.4795</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1808</v>
+        <v>1.5593</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4391</v>
+        <v>3.2051</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3331</v>
+        <v>2.4165</v>
       </c>
       <c r="I19" t="n">
-        <v>1.106</v>
+        <v>0.7887</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5776</v>
+        <v>2.7719</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3507</v>
+        <v>2.004</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2269</v>
+        <v>0.7679</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1385</v>
+        <v>0.4332</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0176</v>
+        <v>0.4125</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1209</v>
+        <v>0.0208</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9585</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9585</v>
+        <v>1.3709</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5044</v>
+        <v>1.7334</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1317</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6361</v>
+        <v>0.9718</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6083</v>
+        <v>-0.3329</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3329</v>
+        <v>0.8837</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2754</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>. SUAREZ HEVIA</t>
+          <t>R. FERNANDEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.0512</v>
+        <v>2.8752</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8407</v>
+        <v>1.9083</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2105</v>
+        <v>0.9669</v>
       </c>
       <c r="G20" t="n">
-        <v>2.0122</v>
+        <v>1.4391</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0926</v>
+        <v>0.3331</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9195</v>
+        <v>1.106</v>
       </c>
       <c r="J20" t="n">
-        <v>3.7527</v>
+        <v>2.5776</v>
       </c>
       <c r="K20" t="n">
-        <v>2.4498</v>
+        <v>1.3507</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3029</v>
+        <v>1.2269</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7406</v>
+        <v>-1.1385</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3572</v>
+        <v>-1.0176</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3834</v>
+        <v>-0.1209</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1751</v>
+        <v>1.9585</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1543</v>
+        <v>1.9585</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1361</v>
+        <v>0.0859</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9328</v>
+        <v>-0.3364</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7967</v>
+        <v>0.4223</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.3329</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9943</v>
+        <v>-2.8653</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5107</v>
+        <v>-1.4084</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4836</v>
+        <v>-1.4569</v>
       </c>
       <c r="G21" t="n">
         <v>-2.1455</v>
@@ -2092,13 +2092,13 @@
         <v>1.9585</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6115</v>
+        <v>-0.4824</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-0.7116</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2025</v>
+        <v>0.2292</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2166</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2244</v>
+        <v>-3.2954</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.6118</v>
+        <v>-4.8165</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3874</v>
+        <v>1.5211</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5116</v>
@@ -2170,13 +2170,13 @@
         <v>1.3709</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5578</v>
+        <v>0.4868</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1476</v>
+        <v>-0.0571</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4102</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>0.2754</v>
@@ -2206,10 +2206,10 @@
         <v>20.5966</v>
       </c>
       <c r="E23" t="n">
-        <v>9.381900000000002</v>
+        <v>9.3818</v>
       </c>
       <c r="F23" t="n">
-        <v>11.2148</v>
+        <v>11.2147</v>
       </c>
       <c r="G23" t="n">
         <v>15.9417</v>
@@ -2239,7 +2239,7 @@
         <v>0.1818</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9793000000000003</v>
+        <v>0.9793000000000007</v>
       </c>
       <c r="Q23" t="n">
         <v>-15.6678</v>
@@ -2254,10 +2254,10 @@
         <v>-1.9674</v>
       </c>
       <c r="U23" t="n">
-        <v>4.816799999999999</v>
+        <v>4.8169</v>
       </c>
       <c r="V23" t="n">
-        <v>0.8262</v>
+        <v>0.8261999999999997</v>
       </c>
       <c r="W23" t="n">
         <v>4.1431</v>
